--- a/data/trans_orig/P1002-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/P1002-Estudios-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que dejo de hacer algunas tareas por problemas emocionales en 2007</t>
+          <t>Población que dejo de hacer algunas tareas por problemas emocionales en 2007 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>84391</t>
+          <t>82140</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>122392</t>
+          <t>121778</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>8,18%</t>
+          <t>7,96%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>11,86%</t>
+          <t>11,8%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>145849</t>
+          <t>144543</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>194514</t>
+          <t>191785</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>11,09%</t>
+          <t>10,99%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>14,79%</t>
+          <t>14,58%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>242165</t>
+          <t>242619</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>301415</t>
+          <t>305749</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>10,32%</t>
+          <t>10,34%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>12,84%</t>
+          <t>13,03%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>909331</t>
+          <t>909945</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>947332</t>
+          <t>949583</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>88,14%</t>
+          <t>88,2%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>91,82%</t>
+          <t>92,04%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1120599</t>
+          <t>1123328</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>1169264</t>
+          <t>1170570</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>85,21%</t>
+          <t>85,42%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>88,91%</t>
+          <t>89,01%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>2045420</t>
+          <t>2041086</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>2104670</t>
+          <t>2104216</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>87,16%</t>
+          <t>86,97%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>89,68%</t>
+          <t>89,66%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>35561</t>
+          <t>34656</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>63540</t>
+          <t>61949</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,1%</t>
+          <t>2,05%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>3,75%</t>
+          <t>3,66%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>78337</t>
+          <t>77271</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>116189</t>
+          <t>117088</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>4,93%</t>
+          <t>4,87%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>7,32%</t>
+          <t>7,37%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>119860</t>
+          <t>119329</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>168728</t>
+          <t>165842</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>3,65%</t>
+          <t>3,64%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>5,14%</t>
+          <t>5,05%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1629873</t>
+          <t>1631464</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1657852</t>
+          <t>1658757</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>96,25%</t>
+          <t>96,34%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>97,9%</t>
+          <t>97,95%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1471484</t>
+          <t>1470585</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1509336</t>
+          <t>1510402</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>92,68%</t>
+          <t>92,63%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>95,07%</t>
+          <t>95,13%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>3112358</t>
+          <t>3115244</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>3161226</t>
+          <t>3161757</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>94,86%</t>
+          <t>94,95%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>96,35%</t>
+          <t>96,36%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>12093</t>
+          <t>11990</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>30761</t>
+          <t>31329</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2,19%</t>
+          <t>2,17%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>5,58%</t>
+          <t>5,68%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>14462</t>
+          <t>13953</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>33204</t>
+          <t>31564</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>3,04%</t>
+          <t>2,93%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>6,97%</t>
+          <t>6,63%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>30784</t>
+          <t>30899</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>56717</t>
+          <t>56196</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>3,0%</t>
+          <t>3,01%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>5,52%</t>
+          <t>5,47%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>520647</t>
+          <t>520079</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>539315</t>
+          <t>539418</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>94,42%</t>
+          <t>94,32%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>97,81%</t>
+          <t>97,83%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>443208</t>
+          <t>444848</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>461950</t>
+          <t>462459</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>93,03%</t>
+          <t>93,37%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>96,96%</t>
+          <t>97,07%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>971103</t>
+          <t>971624</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>997036</t>
+          <t>996921</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>94,48%</t>
+          <t>94,53%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>97,0%</t>
+          <t>96,99%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>146413</t>
+          <t>146756</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>197135</t>
+          <t>198797</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>4,47%</t>
+          <t>4,48%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>6,02%</t>
+          <t>6,07%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>253234</t>
+          <t>254321</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>321680</t>
+          <t>320284</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>7,49%</t>
+          <t>7,53%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>9,52%</t>
+          <t>9,48%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>416591</t>
+          <t>416760</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>501248</t>
+          <t>498152</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1852,7 +1852,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>7,53%</t>
+          <t>7,48%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>3079408</t>
+          <t>3077746</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3130130</t>
+          <t>3129787</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>93,98%</t>
+          <t>93,93%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>95,53%</t>
+          <t>95,52%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>3057517</t>
+          <t>3058913</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>3125963</t>
+          <t>3124876</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>90,48%</t>
+          <t>90,52%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>92,51%</t>
+          <t>92,47%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>6154493</t>
+          <t>6157589</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>6239150</t>
+          <t>6238981</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,7 +1960,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>92,47%</t>
+          <t>92,52%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -2141,7 +2141,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que dejo de hacer algunas tareas por problemas emocionales en 2012</t>
+          <t>Población que dejo de hacer algunas tareas por problemas emocionales en 2012 (tasa de respuesta: 99,94%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2336,12 +2336,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>103878</t>
+          <t>106994</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>149204</t>
+          <t>150270</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2351,12 +2351,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>10,66%</t>
+          <t>10,98%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>15,31%</t>
+          <t>15,42%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2371,12 +2371,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>275864</t>
+          <t>275082</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>339414</t>
+          <t>340291</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2386,12 +2386,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>20,64%</t>
+          <t>20,58%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>25,39%</t>
+          <t>25,46%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2406,12 +2406,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>395838</t>
+          <t>397460</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>470119</t>
+          <t>470339</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2421,12 +2421,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>17,13%</t>
+          <t>17,2%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>20,34%</t>
+          <t>20,35%</t>
         </is>
       </c>
     </row>
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>825439</t>
+          <t>824373</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>870765</t>
+          <t>867649</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2464,12 +2464,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>84,69%</t>
+          <t>84,58%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>89,34%</t>
+          <t>89,02%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2484,12 +2484,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>997328</t>
+          <t>996451</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>1060878</t>
+          <t>1061660</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2499,12 +2499,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>74,61%</t>
+          <t>74,54%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>79,36%</t>
+          <t>79,42%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2519,12 +2519,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1841266</t>
+          <t>1841046</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1915547</t>
+          <t>1913925</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2534,12 +2534,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>79,66%</t>
+          <t>79,65%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>82,87%</t>
+          <t>82,8%</t>
         </is>
       </c>
     </row>
@@ -2679,12 +2679,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>70725</t>
+          <t>71011</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>109889</t>
+          <t>111675</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -2694,12 +2694,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>3,6%</t>
+          <t>3,62%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>5,6%</t>
+          <t>5,69%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -2714,12 +2714,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>142331</t>
+          <t>140829</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>194415</t>
+          <t>194303</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -2729,12 +2729,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>8,1%</t>
+          <t>8,01%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>11,06%</t>
+          <t>11,05%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -2749,12 +2749,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>227003</t>
+          <t>222098</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>298261</t>
+          <t>289403</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -2764,12 +2764,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>6,1%</t>
+          <t>5,97%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>8,02%</t>
+          <t>7,78%</t>
         </is>
       </c>
     </row>
@@ -2792,12 +2792,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1852078</t>
+          <t>1850292</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1891242</t>
+          <t>1890956</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2807,12 +2807,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>94,4%</t>
+          <t>94,31%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>96,4%</t>
+          <t>96,38%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -2827,12 +2827,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1563388</t>
+          <t>1563500</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1615472</t>
+          <t>1616974</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -2842,12 +2842,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>88,94%</t>
+          <t>88,95%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>91,9%</t>
+          <t>91,99%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -2862,12 +2862,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>3421508</t>
+          <t>3430366</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>3492766</t>
+          <t>3497671</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -2877,12 +2877,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>91,98%</t>
+          <t>92,22%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>93,9%</t>
+          <t>94,03%</t>
         </is>
       </c>
     </row>
@@ -3022,12 +3022,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>7816</t>
+          <t>7223</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>26194</t>
+          <t>27102</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3037,12 +3037,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,62%</t>
+          <t>1,5%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>5,44%</t>
+          <t>5,63%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3057,12 +3057,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>13229</t>
+          <t>15206</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>32661</t>
+          <t>34666</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3072,12 +3072,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>2,88%</t>
+          <t>3,32%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>7,12%</t>
+          <t>7,56%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3092,12 +3092,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>24486</t>
+          <t>26032</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>53157</t>
+          <t>52161</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3107,12 +3107,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>2,61%</t>
+          <t>2,77%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>5,66%</t>
+          <t>5,55%</t>
         </is>
       </c>
     </row>
@@ -3135,12 +3135,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>454987</t>
+          <t>454079</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>473365</t>
+          <t>473958</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3150,12 +3150,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>94,56%</t>
+          <t>94,37%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>98,38%</t>
+          <t>98,5%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3170,12 +3170,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>425970</t>
+          <t>423965</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>445402</t>
+          <t>443425</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3185,12 +3185,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>92,88%</t>
+          <t>92,44%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>97,12%</t>
+          <t>96,68%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3205,12 +3205,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>886656</t>
+          <t>887652</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>915327</t>
+          <t>913781</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3220,12 +3220,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>94,34%</t>
+          <t>94,45%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>97,39%</t>
+          <t>97,23%</t>
         </is>
       </c>
     </row>
@@ -3365,12 +3365,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>199284</t>
+          <t>200811</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>265356</t>
+          <t>262456</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3380,12 +3380,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>5,83%</t>
+          <t>5,88%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>7,76%</t>
+          <t>7,68%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3400,12 +3400,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>456083</t>
+          <t>458937</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>539469</t>
+          <t>543010</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3415,12 +3415,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>12,84%</t>
+          <t>12,92%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>15,18%</t>
+          <t>15,28%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3435,12 +3435,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>673897</t>
+          <t>671626</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>776250</t>
+          <t>780492</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3450,12 +3450,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>9,67%</t>
+          <t>9,63%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>11,14%</t>
+          <t>11,2%</t>
         </is>
       </c>
     </row>
@@ -3478,12 +3478,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>3152435</t>
+          <t>3155335</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3218507</t>
+          <t>3216980</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3493,12 +3493,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>92,24%</t>
+          <t>92,32%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>94,17%</t>
+          <t>94,12%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3513,12 +3513,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>3013706</t>
+          <t>3010165</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>3097092</t>
+          <t>3094238</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3528,12 +3528,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>84,82%</t>
+          <t>84,72%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>87,16%</t>
+          <t>87,08%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3548,12 +3548,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>6194716</t>
+          <t>6190474</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>6297069</t>
+          <t>6299340</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3563,12 +3563,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>88,86%</t>
+          <t>88,8%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>90,33%</t>
+          <t>90,37%</t>
         </is>
       </c>
     </row>
@@ -3744,7 +3744,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que dejo de hacer algunas tareas por problemas emocionales en 2016</t>
+          <t>Población que dejo de hacer algunas tareas por problemas emocionales en 2016 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3939,12 +3939,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>54813</t>
+          <t>52932</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>85086</t>
+          <t>85925</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3954,12 +3954,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>7,27%</t>
+          <t>7,02%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>11,28%</t>
+          <t>11,39%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3974,12 +3974,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>177442</t>
+          <t>177190</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>232502</t>
+          <t>230870</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3989,12 +3989,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>17,84%</t>
+          <t>17,81%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>23,38%</t>
+          <t>23,21%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4009,12 +4009,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>242483</t>
+          <t>242854</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>306951</t>
+          <t>304488</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4024,12 +4024,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>13,86%</t>
+          <t>13,89%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>17,55%</t>
+          <t>17,41%</t>
         </is>
       </c>
     </row>
@@ -4052,12 +4052,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>669261</t>
+          <t>668422</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>699534</t>
+          <t>701415</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4067,12 +4067,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>88,72%</t>
+          <t>88,61%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>92,73%</t>
+          <t>92,98%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4087,12 +4087,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>762158</t>
+          <t>763790</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>817218</t>
+          <t>817470</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4102,12 +4102,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>76,62%</t>
+          <t>76,79%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>82,16%</t>
+          <t>82,19%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1442056</t>
+          <t>1444519</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1506524</t>
+          <t>1506153</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4137,12 +4137,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>82,45%</t>
+          <t>82,59%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>86,14%</t>
+          <t>86,11%</t>
         </is>
       </c>
     </row>
@@ -4282,12 +4282,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>77187</t>
+          <t>78026</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>118229</t>
+          <t>118469</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4297,12 +4297,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>3,72%</t>
+          <t>3,76%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>5,69%</t>
+          <t>5,71%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4317,12 +4317,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>125245</t>
+          <t>127464</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>175226</t>
+          <t>175155</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4332,7 +4332,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>6,3%</t>
+          <t>6,41%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -4352,12 +4352,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>212838</t>
+          <t>215427</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>276663</t>
+          <t>276784</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4367,7 +4367,7 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>5,24%</t>
+          <t>5,3%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
@@ -4395,12 +4395,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1958156</t>
+          <t>1957916</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1999198</t>
+          <t>1998359</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4410,12 +4410,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>94,31%</t>
+          <t>94,29%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>96,28%</t>
+          <t>96,24%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4430,12 +4430,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1813074</t>
+          <t>1813145</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1863055</t>
+          <t>1860836</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4450,7 +4450,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>93,7%</t>
+          <t>93,59%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4465,12 +4465,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>3788022</t>
+          <t>3787901</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>3851847</t>
+          <t>3849258</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4485,7 +4485,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>94,76%</t>
+          <t>94,7%</t>
         </is>
       </c>
     </row>
@@ -4625,12 +4625,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>8523</t>
+          <t>8726</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>26427</t>
+          <t>26161</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4640,12 +4640,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,56%</t>
+          <t>1,6%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>4,83%</t>
+          <t>4,78%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4660,12 +4660,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>16780</t>
+          <t>16584</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>36879</t>
+          <t>36209</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4675,12 +4675,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>3,06%</t>
+          <t>3,02%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>6,72%</t>
+          <t>6,59%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4695,12 +4695,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>28959</t>
+          <t>30118</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>55314</t>
+          <t>54935</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4710,12 +4710,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>2,64%</t>
+          <t>2,75%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>5,05%</t>
+          <t>5,01%</t>
         </is>
       </c>
     </row>
@@ -4738,12 +4738,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>520459</t>
+          <t>520725</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>538363</t>
+          <t>538160</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4753,12 +4753,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>95,17%</t>
+          <t>95,22%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>98,44%</t>
+          <t>98,4%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4773,12 +4773,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>512261</t>
+          <t>512931</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>532360</t>
+          <t>532556</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4788,12 +4788,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>93,28%</t>
+          <t>93,41%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>96,94%</t>
+          <t>96,98%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4808,12 +4808,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1040713</t>
+          <t>1041092</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1067068</t>
+          <t>1065909</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4823,12 +4823,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>94,95%</t>
+          <t>94,99%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>97,36%</t>
+          <t>97,25%</t>
         </is>
       </c>
     </row>
@@ -4968,12 +4968,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>156442</t>
+          <t>156583</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>210780</t>
+          <t>209605</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4983,12 +4983,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>4,63%</t>
+          <t>4,64%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>6,24%</t>
+          <t>6,21%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5003,12 +5003,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>339432</t>
+          <t>343280</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>416453</t>
+          <t>417314</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5018,12 +5018,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>9,61%</t>
+          <t>9,72%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>11,79%</t>
+          <t>11,81%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5038,12 +5038,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>511555</t>
+          <t>512918</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>608392</t>
+          <t>607692</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5053,12 +5053,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>7,4%</t>
+          <t>7,42%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>8,8%</t>
+          <t>8,79%</t>
         </is>
       </c>
     </row>
@@ -5081,12 +5081,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>3166838</t>
+          <t>3168013</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3221176</t>
+          <t>3221035</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5096,12 +5096,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>93,76%</t>
+          <t>93,79%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>95,37%</t>
+          <t>95,36%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5116,12 +5116,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>3115647</t>
+          <t>3114786</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>3192668</t>
+          <t>3188820</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5131,12 +5131,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>88,21%</t>
+          <t>88,19%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>90,39%</t>
+          <t>90,28%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5151,12 +5151,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>6301326</t>
+          <t>6302026</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>6398163</t>
+          <t>6396800</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5166,12 +5166,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>91,2%</t>
+          <t>91,21%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>92,6%</t>
+          <t>92,58%</t>
         </is>
       </c>
     </row>
@@ -5347,7 +5347,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que dejo de hacer algunas tareas por problemas emocionales en 2023</t>
+          <t>Población que dejo de hacer algunas tareas por problemas emocionales en 2023 (tasa de respuesta: 99,93%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -5542,12 +5542,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>46838</t>
+          <t>47280</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>72732</t>
+          <t>72890</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -5557,12 +5557,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>9,11%</t>
+          <t>9,19%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>14,14%</t>
+          <t>14,17%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -5577,12 +5577,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>148834</t>
+          <t>150845</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>185837</t>
+          <t>186181</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -5592,12 +5592,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>19,74%</t>
+          <t>20,01%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>24,65%</t>
+          <t>24,69%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5612,12 +5612,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>204366</t>
+          <t>204078</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>250802</t>
+          <t>251617</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -5627,12 +5627,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>16,11%</t>
+          <t>16,09%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>19,77%</t>
+          <t>19,84%</t>
         </is>
       </c>
     </row>
@@ -5655,12 +5655,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>441571</t>
+          <t>441413</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>467465</t>
+          <t>467023</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -5670,12 +5670,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>85,86%</t>
+          <t>85,83%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>90,89%</t>
+          <t>90,81%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -5690,12 +5690,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>568163</t>
+          <t>567819</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>605166</t>
+          <t>603155</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -5705,12 +5705,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>75,35%</t>
+          <t>75,31%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>80,26%</t>
+          <t>79,99%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5725,12 +5725,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1017501</t>
+          <t>1016686</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1063937</t>
+          <t>1064225</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -5740,12 +5740,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>80,23%</t>
+          <t>80,16%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>83,89%</t>
+          <t>83,91%</t>
         </is>
       </c>
     </row>
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>71005</t>
+          <t>69743</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>129322</t>
+          <t>132999</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -5900,12 +5900,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>3,1%</t>
+          <t>3,05%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>5,65%</t>
+          <t>5,81%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5920,12 +5920,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>108789</t>
+          <t>108943</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>178771</t>
+          <t>178903</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -5935,12 +5935,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>4,86%</t>
+          <t>4,87%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>7,99%</t>
+          <t>8,0%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5955,12 +5955,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>199269</t>
+          <t>205847</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>295841</t>
+          <t>295542</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5970,7 +5970,7 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>4,4%</t>
+          <t>4,55%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
@@ -5998,12 +5998,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>2160435</t>
+          <t>2156758</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>2218752</t>
+          <t>2220014</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -6013,12 +6013,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>94,35%</t>
+          <t>94,19%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>96,9%</t>
+          <t>96,95%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -6033,12 +6033,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>2058731</t>
+          <t>2058599</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>2128713</t>
+          <t>2128559</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -6048,12 +6048,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>92,01%</t>
+          <t>92,0%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>95,14%</t>
+          <t>95,13%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6068,12 +6068,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>4231417</t>
+          <t>4231716</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>4327989</t>
+          <t>4321411</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -6088,7 +6088,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>95,6%</t>
+          <t>95,45%</t>
         </is>
       </c>
     </row>
@@ -6228,12 +6228,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>15886</t>
+          <t>16283</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>36704</t>
+          <t>36402</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -6243,12 +6243,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2,46%</t>
+          <t>2,52%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>5,68%</t>
+          <t>5,63%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6263,12 +6263,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>35711</t>
+          <t>34935</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>61093</t>
+          <t>59903</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6278,12 +6278,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>5,41%</t>
+          <t>5,29%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>9,25%</t>
+          <t>9,07%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6298,12 +6298,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>55363</t>
+          <t>55198</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>89127</t>
+          <t>88643</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6313,12 +6313,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>4,24%</t>
+          <t>4,22%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>6,82%</t>
+          <t>6,78%</t>
         </is>
       </c>
     </row>
@@ -6341,12 +6341,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>609919</t>
+          <t>610221</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>630737</t>
+          <t>630340</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -6356,12 +6356,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>94,32%</t>
+          <t>94,37%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>97,54%</t>
+          <t>97,48%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6376,12 +6376,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>599370</t>
+          <t>600560</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>624752</t>
+          <t>625528</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -6391,12 +6391,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>90,75%</t>
+          <t>90,93%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>94,59%</t>
+          <t>94,71%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6411,12 +6411,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1217959</t>
+          <t>1218443</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1251723</t>
+          <t>1251888</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -6426,12 +6426,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>93,18%</t>
+          <t>93,22%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>95,76%</t>
+          <t>95,78%</t>
         </is>
       </c>
     </row>
@@ -6571,12 +6571,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>144411</t>
+          <t>141847</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>220310</t>
+          <t>214515</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -6586,12 +6586,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>4,18%</t>
+          <t>4,11%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>6,38%</t>
+          <t>6,22%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -6606,12 +6606,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>301583</t>
+          <t>295723</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>406681</t>
+          <t>405709</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -6621,12 +6621,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>8,26%</t>
+          <t>8,1%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>11,14%</t>
+          <t>11,11%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -6641,12 +6641,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>476932</t>
+          <t>478279</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>606191</t>
+          <t>605036</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -6656,12 +6656,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>6,71%</t>
+          <t>6,73%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>8,53%</t>
+          <t>8,52%</t>
         </is>
       </c>
     </row>
@@ -6684,12 +6684,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>3230373</t>
+          <t>3236168</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3306272</t>
+          <t>3308836</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -6699,12 +6699,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>93,62%</t>
+          <t>93,78%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>95,82%</t>
+          <t>95,89%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6719,12 +6719,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>3245284</t>
+          <t>3246256</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>3350382</t>
+          <t>3356242</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -6734,12 +6734,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>88,86%</t>
+          <t>88,89%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>91,74%</t>
+          <t>91,9%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6754,12 +6754,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>6496456</t>
+          <t>6497611</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>6625715</t>
+          <t>6624368</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -6769,12 +6769,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>91,47%</t>
+          <t>91,48%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>93,29%</t>
+          <t>93,27%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P1002-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/P1002-Estudios-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>82140</t>
+          <t>84054</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>121778</t>
+          <t>125946</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>7,96%</t>
+          <t>8,15%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>11,8%</t>
+          <t>12,21%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>144543</t>
+          <t>144873</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>191785</t>
+          <t>195443</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>10,99%</t>
+          <t>11,02%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>14,58%</t>
+          <t>14,86%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>242619</t>
+          <t>242722</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>305749</t>
+          <t>304037</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -823,7 +823,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>13,03%</t>
+          <t>12,96%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>909945</t>
+          <t>905777</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>949583</t>
+          <t>947669</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>88,2%</t>
+          <t>87,79%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>92,04%</t>
+          <t>91,85%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1123328</t>
+          <t>1119670</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>1170570</t>
+          <t>1170240</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>85,42%</t>
+          <t>85,14%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>89,01%</t>
+          <t>88,98%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>2041086</t>
+          <t>2042798</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>2104216</t>
+          <t>2104113</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,7 +931,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>86,97%</t>
+          <t>87,04%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>34656</t>
+          <t>34345</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>61949</t>
+          <t>60685</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,05%</t>
+          <t>2,03%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>3,66%</t>
+          <t>3,58%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>77271</t>
+          <t>78642</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>117088</t>
+          <t>116973</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,7 +1126,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>4,87%</t>
+          <t>4,95%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>119329</t>
+          <t>121339</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>165842</t>
+          <t>168042</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>3,64%</t>
+          <t>3,7%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>5,05%</t>
+          <t>5,12%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1631464</t>
+          <t>1632728</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1658757</t>
+          <t>1659068</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>96,34%</t>
+          <t>96,42%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>97,95%</t>
+          <t>97,97%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1470585</t>
+          <t>1470700</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1510402</t>
+          <t>1509031</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1244,7 +1244,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>95,13%</t>
+          <t>95,05%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>3115244</t>
+          <t>3113044</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>3161757</t>
+          <t>3159747</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>94,95%</t>
+          <t>94,88%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>96,36%</t>
+          <t>96,3%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>11990</t>
+          <t>12661</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>31329</t>
+          <t>31412</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2,17%</t>
+          <t>2,3%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>5,68%</t>
+          <t>5,7%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>13953</t>
+          <t>14307</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>31564</t>
+          <t>31974</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>2,93%</t>
+          <t>3,0%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>6,63%</t>
+          <t>6,71%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>30899</t>
+          <t>30834</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>56196</t>
+          <t>57821</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>3,01%</t>
+          <t>3,0%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>5,47%</t>
+          <t>5,63%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>520079</t>
+          <t>519996</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>539418</t>
+          <t>538747</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>94,32%</t>
+          <t>94,3%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>97,83%</t>
+          <t>97,7%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>444848</t>
+          <t>444438</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>462459</t>
+          <t>462105</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>93,37%</t>
+          <t>93,29%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>97,07%</t>
+          <t>97,0%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>971624</t>
+          <t>969999</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>996921</t>
+          <t>996986</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>94,53%</t>
+          <t>94,37%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>96,99%</t>
+          <t>97,0%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>146756</t>
+          <t>148464</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>198797</t>
+          <t>198912</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,7 +1777,7 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>4,48%</t>
+          <t>4,53%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>254321</t>
+          <t>256407</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>320284</t>
+          <t>320052</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>7,53%</t>
+          <t>7,59%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>9,48%</t>
+          <t>9,47%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>416760</t>
+          <t>417963</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>498152</t>
+          <t>503940</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>6,26%</t>
+          <t>6,28%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>7,48%</t>
+          <t>7,57%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>3077746</t>
+          <t>3077631</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3129787</t>
+          <t>3128079</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1895,7 +1895,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>95,52%</t>
+          <t>95,47%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>3058913</t>
+          <t>3059145</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>3124876</t>
+          <t>3122790</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>90,52%</t>
+          <t>90,53%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>92,47%</t>
+          <t>92,41%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>6157589</t>
+          <t>6151801</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>6238981</t>
+          <t>6237778</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>92,52%</t>
+          <t>92,43%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>93,74%</t>
+          <t>93,72%</t>
         </is>
       </c>
     </row>
@@ -2336,12 +2336,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>106994</t>
+          <t>105398</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>150270</t>
+          <t>151245</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2351,12 +2351,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>10,98%</t>
+          <t>10,81%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>15,42%</t>
+          <t>15,52%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2371,12 +2371,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>275082</t>
+          <t>277261</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>340291</t>
+          <t>339487</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2386,12 +2386,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>20,58%</t>
+          <t>20,74%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>25,46%</t>
+          <t>25,4%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2406,12 +2406,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>397460</t>
+          <t>396358</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>470339</t>
+          <t>474061</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2421,12 +2421,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>17,2%</t>
+          <t>17,15%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>20,35%</t>
+          <t>20,51%</t>
         </is>
       </c>
     </row>
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>824373</t>
+          <t>823398</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>867649</t>
+          <t>869245</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2464,12 +2464,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>84,58%</t>
+          <t>84,48%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>89,02%</t>
+          <t>89,19%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2484,12 +2484,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>996451</t>
+          <t>997255</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>1061660</t>
+          <t>1059481</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2499,12 +2499,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>74,54%</t>
+          <t>74,6%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>79,42%</t>
+          <t>79,26%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2519,12 +2519,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1841046</t>
+          <t>1837324</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1913925</t>
+          <t>1915027</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2534,12 +2534,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>79,65%</t>
+          <t>79,49%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>82,8%</t>
+          <t>82,85%</t>
         </is>
       </c>
     </row>
@@ -2679,12 +2679,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>71011</t>
+          <t>69723</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>111675</t>
+          <t>109327</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -2694,12 +2694,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>3,62%</t>
+          <t>3,55%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>5,69%</t>
+          <t>5,57%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -2714,12 +2714,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>140829</t>
+          <t>141796</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>194303</t>
+          <t>192913</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -2729,12 +2729,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>8,01%</t>
+          <t>8,07%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>11,05%</t>
+          <t>10,97%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -2749,12 +2749,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>222098</t>
+          <t>226434</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>289403</t>
+          <t>288140</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -2764,12 +2764,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>5,97%</t>
+          <t>6,09%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>7,78%</t>
+          <t>7,75%</t>
         </is>
       </c>
     </row>
@@ -2792,12 +2792,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1850292</t>
+          <t>1852640</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1890956</t>
+          <t>1892244</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2807,12 +2807,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>94,31%</t>
+          <t>94,43%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>96,38%</t>
+          <t>96,45%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -2827,12 +2827,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1563500</t>
+          <t>1564890</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1616974</t>
+          <t>1616007</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -2842,12 +2842,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>88,95%</t>
+          <t>89,03%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>91,99%</t>
+          <t>91,93%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -2862,12 +2862,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>3430366</t>
+          <t>3431629</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>3497671</t>
+          <t>3493335</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -2877,12 +2877,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>92,22%</t>
+          <t>92,25%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>94,03%</t>
+          <t>93,91%</t>
         </is>
       </c>
     </row>
@@ -3022,12 +3022,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>7223</t>
+          <t>7722</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>27102</t>
+          <t>27180</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3037,12 +3037,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,5%</t>
+          <t>1,6%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>5,63%</t>
+          <t>5,65%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3057,12 +3057,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>15206</t>
+          <t>13658</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>34666</t>
+          <t>33206</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3072,12 +3072,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>3,32%</t>
+          <t>2,98%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>7,56%</t>
+          <t>7,24%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3092,12 +3092,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>26032</t>
+          <t>25478</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>52161</t>
+          <t>52375</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3107,12 +3107,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>2,77%</t>
+          <t>2,71%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>5,55%</t>
+          <t>5,57%</t>
         </is>
       </c>
     </row>
@@ -3135,12 +3135,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>454079</t>
+          <t>454001</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>473958</t>
+          <t>473459</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3150,12 +3150,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>94,37%</t>
+          <t>94,35%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>98,5%</t>
+          <t>98,4%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3170,12 +3170,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>423965</t>
+          <t>425425</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>443425</t>
+          <t>444973</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3185,12 +3185,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>92,44%</t>
+          <t>92,76%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>96,68%</t>
+          <t>97,02%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3205,12 +3205,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>887652</t>
+          <t>887438</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>913781</t>
+          <t>914335</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3220,12 +3220,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>94,45%</t>
+          <t>94,43%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>97,23%</t>
+          <t>97,29%</t>
         </is>
       </c>
     </row>
@@ -3365,12 +3365,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>200811</t>
+          <t>199182</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>262456</t>
+          <t>259231</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3380,12 +3380,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>5,88%</t>
+          <t>5,83%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>7,68%</t>
+          <t>7,58%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3400,12 +3400,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>458937</t>
+          <t>452980</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>543010</t>
+          <t>540161</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3415,12 +3415,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>12,92%</t>
+          <t>12,75%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>15,28%</t>
+          <t>15,2%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3435,12 +3435,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>671626</t>
+          <t>667567</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>780492</t>
+          <t>779420</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3450,12 +3450,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>9,63%</t>
+          <t>9,58%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>11,2%</t>
+          <t>11,18%</t>
         </is>
       </c>
     </row>
@@ -3478,12 +3478,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>3155335</t>
+          <t>3158560</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3216980</t>
+          <t>3218609</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3493,12 +3493,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>92,32%</t>
+          <t>92,42%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>94,12%</t>
+          <t>94,17%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3513,12 +3513,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>3010165</t>
+          <t>3013014</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>3094238</t>
+          <t>3100195</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3528,12 +3528,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>84,72%</t>
+          <t>84,8%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>87,08%</t>
+          <t>87,25%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3548,12 +3548,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>6190474</t>
+          <t>6191546</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>6299340</t>
+          <t>6303399</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3563,12 +3563,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>88,8%</t>
+          <t>88,82%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>90,37%</t>
+          <t>90,42%</t>
         </is>
       </c>
     </row>
@@ -3939,12 +3939,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>52932</t>
+          <t>54762</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>85925</t>
+          <t>85385</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3954,12 +3954,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>7,02%</t>
+          <t>7,26%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>11,39%</t>
+          <t>11,32%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3974,12 +3974,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>177190</t>
+          <t>179931</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>230870</t>
+          <t>233440</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3989,12 +3989,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>17,81%</t>
+          <t>18,09%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>23,21%</t>
+          <t>23,47%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4009,12 +4009,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>242854</t>
+          <t>239794</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>304488</t>
+          <t>305159</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4024,12 +4024,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>13,89%</t>
+          <t>13,71%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>17,41%</t>
+          <t>17,45%</t>
         </is>
       </c>
     </row>
@@ -4052,12 +4052,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>668422</t>
+          <t>668962</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>701415</t>
+          <t>699585</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4067,12 +4067,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>88,61%</t>
+          <t>88,68%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>92,98%</t>
+          <t>92,74%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4087,12 +4087,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>763790</t>
+          <t>761220</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>817470</t>
+          <t>814729</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4102,12 +4102,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>76,79%</t>
+          <t>76,53%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>82,19%</t>
+          <t>81,91%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1444519</t>
+          <t>1443848</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1506153</t>
+          <t>1509213</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4137,12 +4137,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>82,59%</t>
+          <t>82,55%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>86,11%</t>
+          <t>86,29%</t>
         </is>
       </c>
     </row>
@@ -4282,12 +4282,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>78026</t>
+          <t>76950</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>118469</t>
+          <t>116827</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4297,12 +4297,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>3,76%</t>
+          <t>3,71%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>5,71%</t>
+          <t>5,63%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4317,12 +4317,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>127464</t>
+          <t>126319</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>175155</t>
+          <t>173439</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4332,12 +4332,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>6,41%</t>
+          <t>6,35%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>8,81%</t>
+          <t>8,72%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4352,12 +4352,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>215427</t>
+          <t>216973</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>276784</t>
+          <t>279324</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4367,12 +4367,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>5,3%</t>
+          <t>5,34%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>6,81%</t>
+          <t>6,87%</t>
         </is>
       </c>
     </row>
@@ -4395,12 +4395,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1957916</t>
+          <t>1959558</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1998359</t>
+          <t>1999435</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4410,12 +4410,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>94,29%</t>
+          <t>94,37%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>96,24%</t>
+          <t>96,29%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4430,12 +4430,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1813145</t>
+          <t>1814861</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1860836</t>
+          <t>1861981</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4445,12 +4445,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>91,19%</t>
+          <t>91,28%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>93,59%</t>
+          <t>93,65%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4465,12 +4465,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>3787901</t>
+          <t>3785361</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>3849258</t>
+          <t>3847712</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4480,12 +4480,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>93,19%</t>
+          <t>93,13%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>94,7%</t>
+          <t>94,66%</t>
         </is>
       </c>
     </row>
@@ -4625,12 +4625,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>8726</t>
+          <t>8477</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>26161</t>
+          <t>27032</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4640,12 +4640,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>1,55%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>4,78%</t>
+          <t>4,94%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4660,12 +4660,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>16584</t>
+          <t>15611</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>36209</t>
+          <t>36240</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4675,12 +4675,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>3,02%</t>
+          <t>2,84%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>6,59%</t>
+          <t>6,6%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4695,12 +4695,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>30118</t>
+          <t>28436</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>54935</t>
+          <t>53696</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4710,12 +4710,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>2,75%</t>
+          <t>2,59%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>5,01%</t>
+          <t>4,9%</t>
         </is>
       </c>
     </row>
@@ -4738,12 +4738,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>520725</t>
+          <t>519854</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>538160</t>
+          <t>538409</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4753,12 +4753,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>95,22%</t>
+          <t>95,06%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>98,4%</t>
+          <t>98,45%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4773,12 +4773,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>512931</t>
+          <t>512900</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>532556</t>
+          <t>533529</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4788,12 +4788,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>93,41%</t>
+          <t>93,4%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>96,98%</t>
+          <t>97,16%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4808,12 +4808,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1041092</t>
+          <t>1042331</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1065909</t>
+          <t>1067591</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4823,12 +4823,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>94,99%</t>
+          <t>95,1%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>97,25%</t>
+          <t>97,41%</t>
         </is>
       </c>
     </row>
@@ -4968,12 +4968,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>156583</t>
+          <t>158263</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>209605</t>
+          <t>208922</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4983,12 +4983,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>4,64%</t>
+          <t>4,69%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>6,21%</t>
+          <t>6,19%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5003,12 +5003,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>343280</t>
+          <t>340570</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>417314</t>
+          <t>416385</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5018,12 +5018,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>9,72%</t>
+          <t>9,64%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>11,81%</t>
+          <t>11,79%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5038,12 +5038,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>512918</t>
+          <t>518275</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>607692</t>
+          <t>606367</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5053,12 +5053,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>7,42%</t>
+          <t>7,5%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>8,79%</t>
+          <t>8,78%</t>
         </is>
       </c>
     </row>
@@ -5081,12 +5081,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>3168013</t>
+          <t>3168696</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3221035</t>
+          <t>3219355</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5096,12 +5096,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>93,79%</t>
+          <t>93,81%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>95,36%</t>
+          <t>95,31%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5116,12 +5116,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>3114786</t>
+          <t>3115715</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>3188820</t>
+          <t>3191530</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5131,12 +5131,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>88,19%</t>
+          <t>88,21%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>90,28%</t>
+          <t>90,36%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5151,12 +5151,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>6302026</t>
+          <t>6303351</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>6396800</t>
+          <t>6391443</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5166,12 +5166,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>91,21%</t>
+          <t>91,22%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>92,58%</t>
+          <t>92,5%</t>
         </is>
       </c>
     </row>
@@ -5537,32 +5537,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>58575</t>
+          <t>63027</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>47280</t>
+          <t>50233</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>72890</t>
+          <t>76940</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>11,39%</t>
+          <t>10,91%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>9,19%</t>
+          <t>8,69%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>14,17%</t>
+          <t>13,31%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -5572,32 +5572,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>167032</t>
+          <t>178883</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>150845</t>
+          <t>160886</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>186181</t>
+          <t>198301</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>22,15%</t>
+          <t>21,8%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>20,01%</t>
+          <t>19,61%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>24,69%</t>
+          <t>24,17%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5607,32 +5607,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>225606</t>
+          <t>241910</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>204078</t>
+          <t>219085</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>251617</t>
+          <t>268740</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>17,79%</t>
+          <t>17,3%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>16,09%</t>
+          <t>15,67%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>19,84%</t>
+          <t>19,22%</t>
         </is>
       </c>
     </row>
@@ -5650,32 +5650,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>455728</t>
+          <t>514887</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>441413</t>
+          <t>500974</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>467023</t>
+          <t>527681</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>88,61%</t>
+          <t>89,09%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>85,83%</t>
+          <t>86,69%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>90,81%</t>
+          <t>91,31%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -5685,32 +5685,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>586968</t>
+          <t>641570</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>567819</t>
+          <t>622152</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>603155</t>
+          <t>659567</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>77,85%</t>
+          <t>78,2%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>75,31%</t>
+          <t>75,83%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>79,99%</t>
+          <t>80,39%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5720,32 +5720,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>1042697</t>
+          <t>1156457</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1016686</t>
+          <t>1129627</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1064225</t>
+          <t>1179282</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>82,21%</t>
+          <t>82,7%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>80,16%</t>
+          <t>80,78%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>83,91%</t>
+          <t>84,33%</t>
         </is>
       </c>
     </row>
@@ -5763,17 +5763,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>514303</t>
+          <t>577914</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>514303</t>
+          <t>577914</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>514303</t>
+          <t>577914</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -5798,17 +5798,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>754000</t>
+          <t>820453</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>754000</t>
+          <t>820453</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>754000</t>
+          <t>820453</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -5833,17 +5833,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>1268303</t>
+          <t>1398367</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>1268303</t>
+          <t>1398367</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>1268303</t>
+          <t>1398367</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -5880,32 +5880,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>103871</t>
+          <t>112263</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>69743</t>
+          <t>90463</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>132999</t>
+          <t>137510</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>4,54%</t>
+          <t>5,03%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>3,05%</t>
+          <t>4,06%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>5,81%</t>
+          <t>6,17%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5915,32 +5915,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>150521</t>
+          <t>168572</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>108943</t>
+          <t>148009</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>178903</t>
+          <t>194007</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>6,73%</t>
+          <t>7,76%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>4,87%</t>
+          <t>6,82%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>8,0%</t>
+          <t>8,94%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5950,32 +5950,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>254392</t>
+          <t>280835</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>205847</t>
+          <t>248834</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>295542</t>
+          <t>311140</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>5,62%</t>
+          <t>6,38%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>4,55%</t>
+          <t>5,65%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>6,53%</t>
+          <t>7,07%</t>
         </is>
       </c>
     </row>
@@ -5993,32 +5993,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>2185886</t>
+          <t>2117717</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>2156758</t>
+          <t>2092470</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>2220014</t>
+          <t>2139517</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>95,46%</t>
+          <t>94,97%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>94,19%</t>
+          <t>93,83%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>96,95%</t>
+          <t>95,94%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -6028,32 +6028,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>2086981</t>
+          <t>2002502</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>2058599</t>
+          <t>1977067</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>2128559</t>
+          <t>2023065</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>93,27%</t>
+          <t>92,24%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>92,0%</t>
+          <t>91,06%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>95,13%</t>
+          <t>93,18%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6063,32 +6063,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>4272866</t>
+          <t>4120219</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>4231716</t>
+          <t>4089914</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>4321411</t>
+          <t>4152220</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>94,38%</t>
+          <t>93,62%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>93,47%</t>
+          <t>92,93%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>95,45%</t>
+          <t>94,35%</t>
         </is>
       </c>
     </row>
@@ -6106,17 +6106,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>2289757</t>
+          <t>2229980</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2289757</t>
+          <t>2229980</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>2289757</t>
+          <t>2229980</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -6141,17 +6141,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>2237502</t>
+          <t>2171074</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>2237502</t>
+          <t>2171074</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>2237502</t>
+          <t>2171074</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -6176,17 +6176,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>4527258</t>
+          <t>4401054</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>4527258</t>
+          <t>4401054</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>4527258</t>
+          <t>4401054</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -6223,32 +6223,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>24686</t>
+          <t>26814</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>16283</t>
+          <t>16992</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>36402</t>
+          <t>39285</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>3,82%</t>
+          <t>3,77%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2,52%</t>
+          <t>2,39%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>5,63%</t>
+          <t>5,52%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6258,32 +6258,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>46378</t>
+          <t>53955</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>34935</t>
+          <t>42533</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>59903</t>
+          <t>68528</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>7,02%</t>
+          <t>7,34%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>5,29%</t>
+          <t>5,79%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>9,07%</t>
+          <t>9,33%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6293,32 +6293,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>71064</t>
+          <t>80770</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>55198</t>
+          <t>64712</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>88643</t>
+          <t>99169</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>5,44%</t>
+          <t>5,58%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>4,22%</t>
+          <t>4,47%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>6,78%</t>
+          <t>6,86%</t>
         </is>
       </c>
     </row>
@@ -6336,32 +6336,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>621937</t>
+          <t>684773</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>610221</t>
+          <t>672302</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>630340</t>
+          <t>694595</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>96,18%</t>
+          <t>96,23%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>94,37%</t>
+          <t>94,48%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>97,48%</t>
+          <t>97,61%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6371,32 +6371,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>614085</t>
+          <t>680922</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>600560</t>
+          <t>666349</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>625528</t>
+          <t>692344</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>92,98%</t>
+          <t>92,66%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>90,93%</t>
+          <t>90,67%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>94,71%</t>
+          <t>94,21%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6406,32 +6406,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>1236022</t>
+          <t>1365694</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1218443</t>
+          <t>1347295</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1251888</t>
+          <t>1381752</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>94,56%</t>
+          <t>94,42%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>93,22%</t>
+          <t>93,14%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>95,78%</t>
+          <t>95,53%</t>
         </is>
       </c>
     </row>
@@ -6449,17 +6449,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>646623</t>
+          <t>711587</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>646623</t>
+          <t>711587</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>646623</t>
+          <t>711587</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -6484,17 +6484,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>660463</t>
+          <t>734877</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>660463</t>
+          <t>734877</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>660463</t>
+          <t>734877</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -6519,17 +6519,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>1307086</t>
+          <t>1446464</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1307086</t>
+          <t>1446464</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1307086</t>
+          <t>1446464</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -6566,32 +6566,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>187132</t>
+          <t>202105</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>141847</t>
+          <t>178012</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>214515</t>
+          <t>232677</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>5,42%</t>
+          <t>5,74%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>4,11%</t>
+          <t>5,06%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>6,22%</t>
+          <t>6,61%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -6601,32 +6601,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>363931</t>
+          <t>401411</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>295723</t>
+          <t>369502</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>405709</t>
+          <t>435370</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>9,97%</t>
+          <t>10,77%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>8,1%</t>
+          <t>9,92%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>11,11%</t>
+          <t>11,68%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -6636,32 +6636,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>551063</t>
+          <t>603515</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>478279</t>
+          <t>562723</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>605036</t>
+          <t>648209</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>7,76%</t>
+          <t>8,33%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>6,73%</t>
+          <t>7,77%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>8,52%</t>
+          <t>8,95%</t>
         </is>
       </c>
     </row>
@@ -6679,32 +6679,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>3263551</t>
+          <t>3317376</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>3236168</t>
+          <t>3286804</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3308836</t>
+          <t>3341469</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>94,58%</t>
+          <t>94,26%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>93,78%</t>
+          <t>93,39%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>95,89%</t>
+          <t>94,94%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6714,32 +6714,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>3288034</t>
+          <t>3324993</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>3246256</t>
+          <t>3291034</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>3356242</t>
+          <t>3356902</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>90,03%</t>
+          <t>89,23%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>88,89%</t>
+          <t>88,32%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>91,9%</t>
+          <t>90,08%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6749,32 +6749,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>6551584</t>
+          <t>6642370</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>6497611</t>
+          <t>6597676</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>6624368</t>
+          <t>6683162</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>92,24%</t>
+          <t>91,67%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>91,48%</t>
+          <t>91,05%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>93,27%</t>
+          <t>92,23%</t>
         </is>
       </c>
     </row>
@@ -6792,17 +6792,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>3450683</t>
+          <t>3519481</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>3450683</t>
+          <t>3519481</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>3450683</t>
+          <t>3519481</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -6827,17 +6827,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>3651965</t>
+          <t>3726404</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>3651965</t>
+          <t>3726404</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>3651965</t>
+          <t>3726404</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -6862,17 +6862,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>7102647</t>
+          <t>7245885</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>7102647</t>
+          <t>7245885</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>7102647</t>
+          <t>7245885</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
